--- a/Data/Regression Evidence 2025/Workday_NewHire_France_Regression_PK17.xlsx
+++ b/Data/Regression Evidence 2025/Workday_NewHire_France_Regression_PK17.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{99C052E4-845A-49AD-8442-097F3093245C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{DEF63143-068F-45C4-947F-9DE8745CBB9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -256,10 +256,10 @@
     <t>Madame</t>
   </si>
   <si>
-    <t>Christ</t>
-  </si>
-  <si>
-    <t>Wunsch</t>
+    <t>Morton</t>
+  </si>
+  <si>
+    <t>Wyman</t>
   </si>
   <si>
     <t>03 48 29 85 70</t>
@@ -397,13 +397,13 @@
     <t>221 Store Management (Pucyw Zipato (9221018))</t>
   </si>
   <si>
-    <t>Francisco</t>
-  </si>
-  <si>
-    <t>MacGyver</t>
-  </si>
-  <si>
-    <t>Auto 41715071</t>
+    <t>Norene</t>
+  </si>
+  <si>
+    <t>Tromp</t>
+  </si>
+  <si>
+    <t>Auto 23126512</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -503,7 +503,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -541,7 +541,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -614,7 +620,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -708,6 +714,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -990,7 +999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BY36"/>
+  <dimension ref="A1:BY38"/>
   <sheetFormatPr defaultRowHeight="15.65" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.81640625" style="1" customWidth="1"/>
@@ -1309,9 +1318,9 @@
         <v>70</v>
       </c>
       <c r="B2" s="9">
-        <v>10700240</v>
-      </c>
-      <c r="C2" s="33" t="s">
+        <v>10700449</v>
+      </c>
+      <c r="C2" s="34" t="s">
         <v>134</v>
       </c>
       <c r="D2" s="11" t="s">
@@ -1340,7 +1349,7 @@
       </c>
       <c r="L2" s="18">
         <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="M2" s="12" t="s">
         <v>72</v>
@@ -1371,7 +1380,7 @@
       </c>
       <c r="V2" s="18">
         <f t="shared" ref="V2:V3" ca="1" si="1">L2</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="W2" s="17" t="s">
         <v>85</v>
@@ -1417,15 +1426,15 @@
       </c>
       <c r="AK2" s="25">
         <f t="shared" ref="AK2:AK3" ca="1" si="2">V2</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="AL2" s="25">
         <f t="shared" ref="AL2:AL3" ca="1" si="3">V2</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="AM2" s="25">
         <f t="shared" ref="AM2:AM3" ca="1" si="4">V2</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="AN2" s="18" t="str">
         <f t="shared" ref="AN2:AN3" si="5">AG2</f>
@@ -1454,7 +1463,7 @@
       </c>
       <c r="AV2" s="25">
         <f t="shared" ref="AV2:AV3" ca="1" si="6">TODAY()+20</f>
-        <v>45873</v>
+        <v>45894</v>
       </c>
       <c r="AW2" s="12" t="s">
         <v>72</v>
@@ -1464,7 +1473,7 @@
       </c>
       <c r="AY2" s="27" t="str">
         <f ca="1">BB11</f>
-        <v>X2RQBABA76</v>
+        <v>X7RQBABA84</v>
       </c>
       <c r="AZ2" s="25" t="s">
         <v>106</v>
@@ -1534,7 +1543,7 @@
       </c>
       <c r="BV2" s="32">
         <f t="array" aca="1" ref="BV2:BV3" ca="1">_xlfn.RANDARRAY(2,1,12345,99999,TRUE)</f>
-        <v>71467</v>
+        <v>62852</v>
       </c>
       <c r="BW2" s="25">
         <v>44562</v>
@@ -1551,9 +1560,9 @@
         <v>119</v>
       </c>
       <c r="B3" s="9">
-        <v>10700243</v>
-      </c>
-      <c r="C3" s="33" t="s">
+        <v>10700450</v>
+      </c>
+      <c r="C3" s="34" t="s">
         <v>134</v>
       </c>
       <c r="D3" s="11" t="s">
@@ -1582,7 +1591,7 @@
       </c>
       <c r="L3" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="M3" s="12" t="s">
         <v>72</v>
@@ -1613,7 +1622,7 @@
       </c>
       <c r="V3" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="W3" s="17" t="s">
         <v>85</v>
@@ -1659,15 +1668,15 @@
       </c>
       <c r="AK3" s="25">
         <f t="shared" ca="1" si="2"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="AL3" s="25">
         <f t="shared" ca="1" si="3"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="AM3" s="25">
         <f t="shared" ca="1" si="4"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="AN3" s="18" t="str">
         <f t="shared" si="5"/>
@@ -1696,7 +1705,7 @@
       </c>
       <c r="AV3" s="25">
         <f t="shared" ca="1" si="6"/>
-        <v>45873</v>
+        <v>45894</v>
       </c>
       <c r="AW3" s="12" t="s">
         <v>72</v>
@@ -1706,7 +1715,7 @@
       </c>
       <c r="AY3" s="27" t="str">
         <f ca="1">BB12</f>
-        <v>X7RQBABA45</v>
+        <v>X4RQBABA51</v>
       </c>
       <c r="AZ3" s="25" t="s">
         <v>106</v>
@@ -1776,7 +1785,7 @@
       </c>
       <c r="BV3" s="32">
         <f ca="1"/>
-        <v>78129</v>
+        <v>63510</v>
       </c>
       <c r="BW3" s="25">
         <v>44562</v>
@@ -1794,205 +1803,205 @@
     </row>
     <row r="5" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="10"/>
+      <c r="C6" s="33"/>
     </row>
     <row r="7" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="10"/>
+      <c r="C7" s="33"/>
     </row>
     <row r="8" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="10"/>
+      <c r="C8" s="33"/>
     </row>
     <row r="9" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="10"/>
+      <c r="C9" s="33"/>
     </row>
     <row r="10" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="10"/>
+      <c r="C10" s="33"/>
     </row>
     <row r="11" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="10"/>
+      <c r="C11" s="33"/>
       <c r="AX11" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY11" s="2">
         <f t="array" aca="1" ref="AY11:AY30" ca="1">_xlfn.RANDARRAY(20,1,1,9,TRUE)</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AZ11" s="1" t="s">
         <v>133</v>
       </c>
       <c r="BA11" s="2">
         <f t="array" aca="1" ref="BA11:BA30" ca="1">_xlfn.RANDARRAY(20,1,1,99,TRUE)</f>
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="BB11" s="1" t="str">
         <f ca="1">AX11&amp;AY11&amp;AZ11&amp;BA11</f>
-        <v>X2RQBABA76</v>
+        <v>X7RQBABA84</v>
       </c>
     </row>
     <row r="12" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="10"/>
+      <c r="C12" s="33"/>
       <c r="AX12" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY12" s="2">
         <f ca="1"/>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AZ12" s="1" t="s">
         <v>133</v>
       </c>
       <c r="BA12" s="2">
         <f ca="1"/>
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="BB12" s="1" t="str">
         <f t="shared" ref="BB12:BB36" ca="1" si="7">AX12&amp;AY12&amp;AZ12&amp;BA12</f>
-        <v>X7RQBABA45</v>
+        <v>X4RQBABA51</v>
       </c>
     </row>
     <row r="13" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="10"/>
+      <c r="C13" s="33"/>
       <c r="AY13" s="2">
         <f ca="1"/>
         <v>5</v>
       </c>
       <c r="BA13" s="2">
         <f ca="1"/>
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="BB13" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>571</v>
+        <v>599</v>
       </c>
     </row>
     <row r="14" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="10"/>
+      <c r="C14" s="33"/>
       <c r="AX14" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY14" s="2">
         <f ca="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BA14" s="2">
         <f ca="1"/>
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="BB14" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X496</v>
+        <v>X180</v>
       </c>
     </row>
     <row r="15" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="10"/>
+      <c r="C15" s="33"/>
       <c r="AX15" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY15" s="2">
         <f ca="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA15" s="2">
         <f ca="1"/>
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="BB15" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X870</v>
+        <v>X782</v>
       </c>
     </row>
     <row r="16" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="10"/>
+      <c r="C16" s="33"/>
       <c r="AX16" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY16" s="2">
         <f ca="1"/>
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="BA16" s="2">
         <f ca="1"/>
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="BB16" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X943</v>
+        <v>X111</v>
       </c>
     </row>
     <row r="17" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="10"/>
+      <c r="C17" s="33"/>
       <c r="AX17" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY17" s="2">
         <f ca="1"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BA17" s="2">
         <f ca="1"/>
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="BB17" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X14</v>
+        <v>X877</v>
       </c>
     </row>
     <row r="18" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C18" s="10"/>
+      <c r="C18" s="33"/>
       <c r="AX18" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY18" s="2">
         <f ca="1"/>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="BA18" s="2">
         <f ca="1"/>
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="BB18" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X396</v>
+        <v>X933</v>
       </c>
     </row>
     <row r="19" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C19" s="10"/>
+      <c r="C19" s="33"/>
       <c r="AX19" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY19" s="2">
         <f ca="1"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BA19" s="2">
         <f ca="1"/>
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="BB19" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X439</v>
+        <v>X73</v>
       </c>
     </row>
     <row r="20" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C20" s="10"/>
+      <c r="C20" s="33"/>
       <c r="AX20" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY20" s="2">
         <f ca="1"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BA20" s="2">
         <f ca="1"/>
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="BB20" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X669</v>
+        <v>X159</v>
       </c>
     </row>
     <row r="21" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="10"/>
+      <c r="C21" s="33"/>
       <c r="AX21" s="1" t="s">
         <v>132</v>
       </c>
@@ -2002,15 +2011,15 @@
       </c>
       <c r="BA21" s="2">
         <f ca="1"/>
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="BB21" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X169</v>
+        <v>X191</v>
       </c>
     </row>
     <row r="22" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C22" s="10"/>
+      <c r="C22" s="33"/>
       <c r="AX22" s="1" t="s">
         <v>132</v>
       </c>
@@ -2020,69 +2029,69 @@
       </c>
       <c r="BA22" s="2">
         <f ca="1"/>
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="BB22" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X873</v>
+        <v>X820</v>
       </c>
     </row>
     <row r="23" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="10"/>
+      <c r="C23" s="33"/>
       <c r="AX23" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY23" s="2">
         <f ca="1"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BA23" s="2">
         <f ca="1"/>
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="BB23" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X627</v>
+        <v>X170</v>
       </c>
     </row>
     <row r="24" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C24" s="10"/>
+      <c r="C24" s="33"/>
       <c r="AX24" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY24" s="2">
         <f ca="1"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BA24" s="2">
         <f ca="1"/>
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="BB24" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X857</v>
+        <v>X169</v>
       </c>
     </row>
     <row r="25" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C25" s="10"/>
+      <c r="C25" s="33"/>
       <c r="AX25" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY25" s="2">
         <f ca="1"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA25" s="2">
         <f ca="1"/>
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="BB25" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X747</v>
+        <v>X987</v>
       </c>
     </row>
     <row r="26" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C26" s="10"/>
+      <c r="C26" s="33"/>
       <c r="AX26" s="1" t="s">
         <v>132</v>
       </c>
@@ -2092,87 +2101,87 @@
       </c>
       <c r="BA26" s="2">
         <f ca="1"/>
-        <v>94</v>
+        <v>11</v>
       </c>
       <c r="BB26" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X194</v>
+        <v>X111</v>
       </c>
     </row>
     <row r="27" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C27" s="10"/>
+      <c r="C27" s="33"/>
       <c r="AX27" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY27" s="2">
         <f ca="1"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BA27" s="2">
         <f ca="1"/>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="BB27" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X45</v>
+        <v>X812</v>
       </c>
     </row>
     <row r="28" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C28" s="10"/>
+      <c r="C28" s="33"/>
       <c r="AX28" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY28" s="2">
         <f ca="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BA28" s="2">
         <f ca="1"/>
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="BB28" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X551</v>
+        <v>X227</v>
       </c>
     </row>
     <row r="29" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C29" s="10"/>
+      <c r="C29" s="33"/>
       <c r="AX29" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY29" s="2">
         <f ca="1"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BA29" s="2">
         <f ca="1"/>
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="BB29" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X660</v>
+        <v>X186</v>
       </c>
     </row>
     <row r="30" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C30" s="10"/>
+      <c r="C30" s="33"/>
       <c r="AX30" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY30" s="2">
         <f ca="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA30" s="2">
         <f ca="1"/>
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="BB30" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X651</v>
+        <v>X828</v>
       </c>
     </row>
     <row r="31" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C31" s="10"/>
+      <c r="C31" s="33"/>
       <c r="AX31" s="1" t="s">
         <v>132</v>
       </c>
@@ -2182,7 +2191,7 @@
       </c>
     </row>
     <row r="32" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C32" s="10"/>
+      <c r="C32" s="33"/>
       <c r="AX32" s="1" t="s">
         <v>132</v>
       </c>
@@ -2192,7 +2201,7 @@
       </c>
     </row>
     <row r="33" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C33" s="10"/>
+      <c r="C33" s="33"/>
       <c r="AX33" s="1" t="s">
         <v>132</v>
       </c>
@@ -2202,7 +2211,7 @@
       </c>
     </row>
     <row r="34" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C34" s="10"/>
+      <c r="C34" s="33"/>
       <c r="AX34" s="1" t="s">
         <v>132</v>
       </c>
@@ -2212,7 +2221,7 @@
       </c>
     </row>
     <row r="35" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C35" s="10"/>
+      <c r="C35" s="33"/>
       <c r="AX35" s="1" t="s">
         <v>132</v>
       </c>
@@ -2222,11 +2231,17 @@
       </c>
     </row>
     <row r="36" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C36" s="10"/>
+      <c r="C36" s="33"/>
       <c r="BB36" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
+    </row>
+    <row r="37" spans="3:54" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C37" s="33"/>
+    </row>
+    <row r="38" spans="3:54" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C38" s="33"/>
     </row>
   </sheetData>
   <dataValidations count="1">
